--- a/data_lake/freight/KOBC Container Composite Index.xlsx
+++ b/data_lake/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F525C93-CCCF-44AC-A83F-CD1F13C6BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3C726-FB59-4742-9263-9E8C326F5B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -893,6 +893,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2042,6 +2045,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3191,6 +3197,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4340,6 +4349,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5489,6 +5501,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6637,6 +6652,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7789,6 +7807,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8940,6 +8961,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10091,6 +10115,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11242,6 +11269,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12392,6 +12422,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13560,6 +13593,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14712,6 +14748,9 @@
                 <c:pt idx="182">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15863,6 +15902,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17591,7 +17633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S184"/>
+  <dimension ref="A1:S185"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
@@ -28077,6 +28119,20 @@
       </c>
       <c r="R184" s="13">
         <v>1125</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A185" s="10">
+        <v>46216</v>
+      </c>
+      <c r="B185" s="10">
+        <v>46216</v>
+      </c>
+      <c r="C185" s="11">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/KOBC Container Composite Index.xlsx
+++ b/data_lake/freight/KOBC Container Composite Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3C726-FB59-4742-9263-9E8C326F5B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5EC175-9CF7-4181-8488-3002799A56CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -123,11 +123,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -172,14 +172,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -187,7 +187,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -220,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -243,31 +243,31 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -275,9 +275,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -295,7 +295,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -903,7 +903,7 @@
             <c:numRef>
               <c:f>KCCI!$E$2:$E$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
@@ -1453,6 +1453,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>4330</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2055,7 +2058,7 @@
             <c:numRef>
               <c:f>KCCI!$F$2:$F$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
@@ -2605,6 +2608,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>6922</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3207,7 +3213,7 @@
             <c:numRef>
               <c:f>KCCI!$G$2:$G$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
@@ -3757,6 +3763,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>8421</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>8523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4359,7 +4368,7 @@
             <c:numRef>
               <c:f>KCCI!$H$2:$H$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
@@ -4909,6 +4918,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>5332</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5426</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5511,7 +5523,7 @@
             <c:numRef>
               <c:f>KCCI!$I$2:$I$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
@@ -6061,6 +6073,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>6468</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6569</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6663,7 +6678,7 @@
             <c:numRef>
               <c:f>KCCI!$J$2:$J$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
@@ -7213,6 +7228,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>7164</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7817,7 +7835,7 @@
             <c:numRef>
               <c:f>KCCI!$K$2:$K$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
@@ -8367,6 +8385,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>3574</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3857</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8971,7 +8992,7 @@
             <c:numRef>
               <c:f>KCCI!$L$2:$L$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
@@ -9521,6 +9542,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>7854</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7554</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10125,7 +10149,7 @@
             <c:numRef>
               <c:f>KCCI!$M$2:$M$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
@@ -10675,6 +10699,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>5851</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11279,7 +11306,7 @@
             <c:numRef>
               <c:f>KCCI!$N$2:$N$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
@@ -11829,6 +11856,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>3602</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3636</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12433,7 +12463,7 @@
             <c:numRef>
               <c:f>KCCI!$O$2:$O$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
@@ -12983,6 +13013,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>5419</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5399</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13603,7 +13636,7 @@
             <c:numRef>
               <c:f>KCCI!$P$2:$P$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
@@ -14152,6 +14185,9 @@
                   <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="182">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="183">
                   <c:v>57</c:v>
                 </c:pt>
               </c:numCache>
@@ -14758,7 +14794,7 @@
             <c:numRef>
               <c:f>KCCI!$Q$2:$Q$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
@@ -15307,6 +15343,9 @@
                   <c:v>222</c:v>
                 </c:pt>
                 <c:pt idx="182">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="183">
                   <c:v>239</c:v>
                 </c:pt>
               </c:numCache>
@@ -15913,7 +15952,7 @@
             <c:numRef>
               <c:f>KCCI!$R$2:$R$11164</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
@@ -16463,6 +16502,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>1125</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1137</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16562,7 +16604,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -16604,7 +16646,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -17337,9 +17379,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -17377,7 +17419,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -17483,7 +17525,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -17625,7 +17667,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -17634,26 +17676,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
   <dimension ref="A1:S185"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="9"/>
+    <col min="1" max="1" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.08984375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -17709,7 +17751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19">
       <c r="A2" s="10">
         <v>44872</v>
       </c>
@@ -17766,7 +17808,7 @@
       </c>
       <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19">
       <c r="A3" s="10">
         <v>44879</v>
       </c>
@@ -17823,7 +17865,7 @@
       </c>
       <c r="S3" s="14"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19">
       <c r="A4" s="10">
         <v>44886</v>
       </c>
@@ -17880,7 +17922,7 @@
       </c>
       <c r="S4" s="14"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19">
       <c r="A5" s="10">
         <v>44893</v>
       </c>
@@ -17937,7 +17979,7 @@
       </c>
       <c r="S5" s="14"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19">
       <c r="A6" s="10">
         <v>44900</v>
       </c>
@@ -17994,7 +18036,7 @@
       </c>
       <c r="S6" s="14"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19">
       <c r="A7" s="10">
         <v>44907</v>
       </c>
@@ -18051,7 +18093,7 @@
       </c>
       <c r="S7" s="14"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19">
       <c r="A8" s="10">
         <v>44914</v>
       </c>
@@ -18108,7 +18150,7 @@
       </c>
       <c r="S8" s="14"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19">
       <c r="A9" s="10">
         <v>44921</v>
       </c>
@@ -18165,7 +18207,7 @@
       </c>
       <c r="S9" s="14"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19">
       <c r="A10" s="10">
         <v>44928</v>
       </c>
@@ -18222,7 +18264,7 @@
       </c>
       <c r="S10" s="14"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19">
       <c r="A11" s="10">
         <v>44935</v>
       </c>
@@ -18279,7 +18321,7 @@
       </c>
       <c r="S11" s="14"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19">
       <c r="A12" s="10">
         <v>44942</v>
       </c>
@@ -18336,7 +18378,7 @@
       </c>
       <c r="S12" s="14"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19">
       <c r="A13" s="10">
         <v>44951</v>
       </c>
@@ -18393,7 +18435,7 @@
       </c>
       <c r="S13" s="14"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19">
       <c r="A14" s="10">
         <v>44956</v>
       </c>
@@ -18450,7 +18492,7 @@
       </c>
       <c r="S14" s="14"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19">
       <c r="A15" s="10">
         <v>44963</v>
       </c>
@@ -18507,7 +18549,7 @@
       </c>
       <c r="S15" s="14"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19">
       <c r="A16" s="10">
         <v>44970</v>
       </c>
@@ -18564,7 +18606,7 @@
       </c>
       <c r="S16" s="14"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17" s="10">
         <v>44977</v>
       </c>
@@ -18621,7 +18663,7 @@
       </c>
       <c r="S17" s="14"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18" s="10">
         <v>44984</v>
       </c>
@@ -18678,7 +18720,7 @@
       </c>
       <c r="S18" s="14"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19" s="10">
         <v>44991</v>
       </c>
@@ -18735,7 +18777,7 @@
       </c>
       <c r="S19" s="14"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20" s="10">
         <v>44998</v>
       </c>
@@ -18792,7 +18834,7 @@
       </c>
       <c r="S20" s="14"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21" s="10">
         <v>45005</v>
       </c>
@@ -18849,7 +18891,7 @@
       </c>
       <c r="S21" s="14"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22" s="10">
         <v>45012</v>
       </c>
@@ -18906,7 +18948,7 @@
       </c>
       <c r="S22" s="14"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23" s="10">
         <v>45019</v>
       </c>
@@ -18963,7 +19005,7 @@
       </c>
       <c r="S23" s="14"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24" s="10">
         <v>45026</v>
       </c>
@@ -19020,7 +19062,7 @@
       </c>
       <c r="S24" s="14"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25" s="10">
         <v>45033</v>
       </c>
@@ -19077,7 +19119,7 @@
       </c>
       <c r="S25" s="14"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26" s="10">
         <v>45040</v>
       </c>
@@ -19134,7 +19176,7 @@
       </c>
       <c r="S26" s="14"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27" s="10">
         <v>45048</v>
       </c>
@@ -19191,7 +19233,7 @@
       </c>
       <c r="S27" s="14"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28" s="10">
         <v>45054</v>
       </c>
@@ -19248,7 +19290,7 @@
       </c>
       <c r="S28" s="14"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29" s="10">
         <v>45061</v>
       </c>
@@ -19305,7 +19347,7 @@
       </c>
       <c r="S29" s="14"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30" s="10">
         <v>45068</v>
       </c>
@@ -19362,7 +19404,7 @@
       </c>
       <c r="S30" s="14"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31" s="10">
         <v>45076</v>
       </c>
@@ -19419,7 +19461,7 @@
       </c>
       <c r="S31" s="14"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32" s="10">
         <v>45082</v>
       </c>
@@ -19476,7 +19518,7 @@
       </c>
       <c r="S32" s="14"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33" s="10">
         <v>45089</v>
       </c>
@@ -19533,7 +19575,7 @@
       </c>
       <c r="S33" s="14"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34" s="10">
         <v>45096</v>
       </c>
@@ -19590,7 +19632,7 @@
       </c>
       <c r="S34" s="14"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35" s="10">
         <v>45103</v>
       </c>
@@ -19647,7 +19689,7 @@
       </c>
       <c r="S35" s="14"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36" s="10">
         <v>45110</v>
       </c>
@@ -19704,7 +19746,7 @@
       </c>
       <c r="S36" s="14"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37" s="10">
         <v>45117</v>
       </c>
@@ -19761,7 +19803,7 @@
       </c>
       <c r="S37" s="14"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38" s="10">
         <v>45124</v>
       </c>
@@ -19818,7 +19860,7 @@
       </c>
       <c r="S38" s="14"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39" s="10">
         <v>45131</v>
       </c>
@@ -19875,7 +19917,7 @@
       </c>
       <c r="S39" s="14"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40" s="10">
         <v>45138</v>
       </c>
@@ -19932,7 +19974,7 @@
       </c>
       <c r="S40" s="14"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41" s="10">
         <v>45145</v>
       </c>
@@ -19989,7 +20031,7 @@
       </c>
       <c r="S41" s="14"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42" s="10">
         <v>45152</v>
       </c>
@@ -20046,7 +20088,7 @@
       </c>
       <c r="S42" s="14"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43" s="10">
         <v>45159</v>
       </c>
@@ -20103,7 +20145,7 @@
       </c>
       <c r="S43" s="14"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44" s="10">
         <v>45166</v>
       </c>
@@ -20160,7 +20202,7 @@
       </c>
       <c r="S44" s="14"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45" s="10">
         <v>45173</v>
       </c>
@@ -20217,7 +20259,7 @@
       </c>
       <c r="S45" s="14"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46" s="10">
         <v>45180</v>
       </c>
@@ -20274,7 +20316,7 @@
       </c>
       <c r="S46" s="14"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47" s="10">
         <v>45187</v>
       </c>
@@ -20331,7 +20373,7 @@
       </c>
       <c r="S47" s="14"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48" s="10">
         <v>45194</v>
       </c>
@@ -20388,7 +20430,7 @@
       </c>
       <c r="S48" s="14"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49" s="10">
         <v>45209</v>
       </c>
@@ -20445,7 +20487,7 @@
       </c>
       <c r="S49" s="14"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50" s="10">
         <v>45215</v>
       </c>
@@ -20502,7 +20544,7 @@
       </c>
       <c r="S50" s="14"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51" s="10">
         <v>45222</v>
       </c>
@@ -20559,7 +20601,7 @@
       </c>
       <c r="S51" s="14"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52" s="10">
         <v>45229</v>
       </c>
@@ -20616,7 +20658,7 @@
       </c>
       <c r="S52" s="14"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53" s="10">
         <v>45236</v>
       </c>
@@ -20673,7 +20715,7 @@
       </c>
       <c r="S53" s="14"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54" s="10">
         <v>45243</v>
       </c>
@@ -20730,7 +20772,7 @@
       </c>
       <c r="S54" s="14"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55" s="10">
         <v>45250</v>
       </c>
@@ -20787,7 +20829,7 @@
       </c>
       <c r="S55" s="14"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56" s="10">
         <v>45257</v>
       </c>
@@ -20844,7 +20886,7 @@
       </c>
       <c r="S56" s="14"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57" s="10">
         <v>45264</v>
       </c>
@@ -20901,7 +20943,7 @@
       </c>
       <c r="S57" s="14"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58" s="10">
         <v>45271</v>
       </c>
@@ -20958,7 +21000,7 @@
       </c>
       <c r="S58" s="14"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59" s="10">
         <v>45278</v>
       </c>
@@ -21015,7 +21057,7 @@
       </c>
       <c r="S59" s="14"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60" s="10">
         <v>45286</v>
       </c>
@@ -21072,7 +21114,7 @@
       </c>
       <c r="S60" s="14"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61" s="10">
         <v>45293</v>
       </c>
@@ -21129,7 +21171,7 @@
       </c>
       <c r="S61" s="14"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62" s="10">
         <v>45299</v>
       </c>
@@ -21186,7 +21228,7 @@
       </c>
       <c r="S62" s="14"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63" s="10">
         <v>45306</v>
       </c>
@@ -21243,7 +21285,7 @@
       </c>
       <c r="S63" s="14"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64" s="10">
         <v>45313</v>
       </c>
@@ -21300,7 +21342,7 @@
       </c>
       <c r="S64" s="14"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65" s="10">
         <v>45320</v>
       </c>
@@ -21357,7 +21399,7 @@
       </c>
       <c r="S65" s="14"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66" s="10">
         <v>45327</v>
       </c>
@@ -21414,7 +21456,7 @@
       </c>
       <c r="S66" s="14"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67" s="10">
         <v>45335</v>
       </c>
@@ -21471,7 +21513,7 @@
       </c>
       <c r="S67" s="14"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68" s="10">
         <v>45341</v>
       </c>
@@ -21528,7 +21570,7 @@
       </c>
       <c r="S68" s="14"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69" s="10">
         <v>45348</v>
       </c>
@@ -21585,7 +21627,7 @@
       </c>
       <c r="S69" s="14"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70" s="10">
         <v>45355</v>
       </c>
@@ -21642,7 +21684,7 @@
       </c>
       <c r="S70" s="14"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71" s="10">
         <v>45362</v>
       </c>
@@ -21699,7 +21741,7 @@
       </c>
       <c r="S71" s="14"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72" s="10">
         <v>45369</v>
       </c>
@@ -21756,7 +21798,7 @@
       </c>
       <c r="S72" s="14"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73" s="10">
         <v>45376</v>
       </c>
@@ -21813,7 +21855,7 @@
       </c>
       <c r="S73" s="14"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74" s="10">
         <v>45383</v>
       </c>
@@ -21870,7 +21912,7 @@
       </c>
       <c r="S74" s="14"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75" s="10">
         <v>45390</v>
       </c>
@@ -21927,7 +21969,7 @@
       </c>
       <c r="S75" s="14"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76" s="10">
         <v>45397</v>
       </c>
@@ -21984,7 +22026,7 @@
       </c>
       <c r="S76" s="14"/>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77" s="10">
         <v>45404</v>
       </c>
@@ -22041,7 +22083,7 @@
       </c>
       <c r="S77" s="14"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78" s="10">
         <v>45411</v>
       </c>
@@ -22098,7 +22140,7 @@
       </c>
       <c r="S78" s="14"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79" s="10">
         <v>45419</v>
       </c>
@@ -22155,7 +22197,7 @@
       </c>
       <c r="S79" s="14"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80" s="10">
         <v>45425</v>
       </c>
@@ -22212,7 +22254,7 @@
       </c>
       <c r="S80" s="14"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19">
       <c r="A81" s="10">
         <v>45432</v>
       </c>
@@ -22269,7 +22311,7 @@
       </c>
       <c r="S81" s="14"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19">
       <c r="A82" s="10">
         <v>45439</v>
       </c>
@@ -22326,7 +22368,7 @@
       </c>
       <c r="S82" s="14"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19">
       <c r="A83" s="10">
         <v>45446</v>
       </c>
@@ -22383,7 +22425,7 @@
       </c>
       <c r="S83" s="14"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19">
       <c r="A84" s="10">
         <v>45453</v>
       </c>
@@ -22440,7 +22482,7 @@
       </c>
       <c r="S84" s="14"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19">
       <c r="A85" s="10">
         <v>45460</v>
       </c>
@@ -22497,7 +22539,7 @@
       </c>
       <c r="S85" s="14"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19">
       <c r="A86" s="10">
         <v>45467</v>
       </c>
@@ -22554,7 +22596,7 @@
       </c>
       <c r="S86" s="14"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19">
       <c r="A87" s="10">
         <v>45474</v>
       </c>
@@ -22611,7 +22653,7 @@
       </c>
       <c r="S87" s="14"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19">
       <c r="A88" s="10">
         <v>45481</v>
       </c>
@@ -22668,7 +22710,7 @@
       </c>
       <c r="S88" s="14"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19">
       <c r="A89" s="10">
         <v>45488</v>
       </c>
@@ -22725,7 +22767,7 @@
       </c>
       <c r="S89" s="14"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19">
       <c r="A90" s="10">
         <v>45495</v>
       </c>
@@ -22782,7 +22824,7 @@
       </c>
       <c r="S90" s="14"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19">
       <c r="A91" s="10">
         <v>45502</v>
       </c>
@@ -22839,7 +22881,7 @@
       </c>
       <c r="S91" s="14"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19">
       <c r="A92" s="10">
         <v>45509</v>
       </c>
@@ -22896,7 +22938,7 @@
       </c>
       <c r="S92" s="14"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19">
       <c r="A93" s="10">
         <v>45516</v>
       </c>
@@ -22953,7 +22995,7 @@
       </c>
       <c r="S93" s="14"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19">
       <c r="A94" s="10">
         <v>45523</v>
       </c>
@@ -23010,7 +23052,7 @@
       </c>
       <c r="S94" s="14"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19">
       <c r="A95" s="10">
         <v>45530</v>
       </c>
@@ -23067,7 +23109,7 @@
       </c>
       <c r="S95" s="14"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19">
       <c r="A96" s="10">
         <v>45537</v>
       </c>
@@ -23124,7 +23166,7 @@
       </c>
       <c r="S96" s="14"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19">
       <c r="A97" s="10">
         <v>45544</v>
       </c>
@@ -23181,7 +23223,7 @@
       </c>
       <c r="S97" s="14"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19">
       <c r="A98" s="10">
         <v>45558</v>
       </c>
@@ -23238,7 +23280,7 @@
       </c>
       <c r="S98" s="14"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19">
       <c r="A99" s="10">
         <v>45565</v>
       </c>
@@ -23295,7 +23337,7 @@
       </c>
       <c r="S99" s="14"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19">
       <c r="A100" s="10">
         <v>45572</v>
       </c>
@@ -23352,7 +23394,7 @@
       </c>
       <c r="S100" s="14"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19">
       <c r="A101" s="10">
         <v>45579</v>
       </c>
@@ -23409,7 +23451,7 @@
       </c>
       <c r="S101" s="14"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19">
       <c r="A102" s="10">
         <v>45586</v>
       </c>
@@ -23466,7 +23508,7 @@
       </c>
       <c r="S102" s="14"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19">
       <c r="A103" s="10">
         <v>45593</v>
       </c>
@@ -23523,7 +23565,7 @@
       </c>
       <c r="S103" s="14"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19">
       <c r="A104" s="10">
         <v>45600</v>
       </c>
@@ -23580,7 +23622,7 @@
       </c>
       <c r="S104" s="14"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19">
       <c r="A105" s="10">
         <v>45607</v>
       </c>
@@ -23637,7 +23679,7 @@
       </c>
       <c r="S105" s="14"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19">
       <c r="A106" s="10">
         <v>45614</v>
       </c>
@@ -23694,7 +23736,7 @@
       </c>
       <c r="S106" s="14"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19">
       <c r="A107" s="10">
         <v>45621</v>
       </c>
@@ -23751,7 +23793,7 @@
       </c>
       <c r="S107" s="14"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19">
       <c r="A108" s="10">
         <v>45628</v>
       </c>
@@ -23808,7 +23850,7 @@
       </c>
       <c r="S108" s="14"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19">
       <c r="A109" s="10">
         <v>45635</v>
       </c>
@@ -23865,7 +23907,7 @@
       </c>
       <c r="S109" s="14"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19">
       <c r="A110" s="10">
         <v>45642</v>
       </c>
@@ -23922,7 +23964,7 @@
       </c>
       <c r="S110" s="14"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19">
       <c r="A111" s="10">
         <v>45649</v>
       </c>
@@ -23979,7 +24021,7 @@
       </c>
       <c r="S111" s="14"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19">
       <c r="A112" s="10">
         <v>45656</v>
       </c>
@@ -24036,7 +24078,7 @@
       </c>
       <c r="S112" s="14"/>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19">
       <c r="A113" s="10">
         <v>45663</v>
       </c>
@@ -24093,7 +24135,7 @@
       </c>
       <c r="S113" s="14"/>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19">
       <c r="A114" s="10">
         <v>45670</v>
       </c>
@@ -24150,7 +24192,7 @@
       </c>
       <c r="S114" s="14"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19">
       <c r="A115" s="10">
         <v>45677</v>
       </c>
@@ -24207,7 +24249,7 @@
       </c>
       <c r="S115" s="14"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19">
       <c r="A116" s="10">
         <v>45691</v>
       </c>
@@ -24264,7 +24306,7 @@
       </c>
       <c r="S116" s="14"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19">
       <c r="A117" s="10">
         <v>45698</v>
       </c>
@@ -24321,7 +24363,7 @@
       </c>
       <c r="S117" s="14"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19">
       <c r="A118" s="10">
         <v>45705</v>
       </c>
@@ -24378,7 +24420,7 @@
       </c>
       <c r="S118" s="14"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19">
       <c r="A119" s="10">
         <v>45712</v>
       </c>
@@ -24435,7 +24477,7 @@
       </c>
       <c r="S119" s="14"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19">
       <c r="A120" s="10">
         <v>45720</v>
       </c>
@@ -24492,7 +24534,7 @@
       </c>
       <c r="S120" s="14"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19">
       <c r="A121" s="10">
         <v>45726</v>
       </c>
@@ -24549,7 +24591,7 @@
       </c>
       <c r="S121" s="14"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19">
       <c r="A122" s="10">
         <v>45733</v>
       </c>
@@ -24606,7 +24648,7 @@
       </c>
       <c r="S122" s="14"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19">
       <c r="A123" s="10">
         <v>45740</v>
       </c>
@@ -24663,7 +24705,7 @@
       </c>
       <c r="S123" s="14"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19">
       <c r="A124" s="10">
         <v>45747</v>
       </c>
@@ -24720,7 +24762,7 @@
       </c>
       <c r="S124" s="14"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19">
       <c r="A125" s="10">
         <v>45754</v>
       </c>
@@ -24777,7 +24819,7 @@
       </c>
       <c r="S125" s="14"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19">
       <c r="A126" s="10">
         <v>45761</v>
       </c>
@@ -24834,7 +24876,7 @@
       </c>
       <c r="S126" s="14"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19">
       <c r="A127" s="10">
         <v>45768</v>
       </c>
@@ -24891,7 +24933,7 @@
       </c>
       <c r="S127" s="14"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19">
       <c r="A128" s="10">
         <v>45775</v>
       </c>
@@ -24948,7 +24990,7 @@
       </c>
       <c r="S128" s="14"/>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19">
       <c r="A129" s="10">
         <v>45789</v>
       </c>
@@ -25005,7 +25047,7 @@
       </c>
       <c r="S129" s="14"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19">
       <c r="A130" s="10">
         <v>45796</v>
       </c>
@@ -25062,7 +25104,7 @@
       </c>
       <c r="S130" s="14"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19">
       <c r="A131" s="10">
         <v>45803</v>
       </c>
@@ -25119,7 +25161,7 @@
       </c>
       <c r="S131" s="14"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19">
       <c r="A132" s="10">
         <v>45810</v>
       </c>
@@ -25176,7 +25218,7 @@
       </c>
       <c r="S132" s="14"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19">
       <c r="A133" s="10">
         <v>45817</v>
       </c>
@@ -25233,7 +25275,7 @@
       </c>
       <c r="S133" s="14"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19">
       <c r="A134" s="10">
         <v>45824</v>
       </c>
@@ -25290,7 +25332,7 @@
       </c>
       <c r="S134" s="14"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19">
       <c r="A135" s="10">
         <v>45831</v>
       </c>
@@ -25347,7 +25389,7 @@
       </c>
       <c r="S135" s="14"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19">
       <c r="A136" s="10">
         <v>45838</v>
       </c>
@@ -25404,7 +25446,7 @@
       </c>
       <c r="S136" s="14"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19">
       <c r="A137" s="10">
         <v>45845</v>
       </c>
@@ -25461,7 +25503,7 @@
       </c>
       <c r="S137" s="14"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19">
       <c r="A138" s="10">
         <v>45852</v>
       </c>
@@ -25518,7 +25560,7 @@
       </c>
       <c r="S138" s="14"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19">
       <c r="A139" s="10">
         <v>45859</v>
       </c>
@@ -25575,7 +25617,7 @@
       </c>
       <c r="S139" s="14"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19">
       <c r="A140" s="10">
         <v>45866</v>
       </c>
@@ -25632,7 +25674,7 @@
       </c>
       <c r="S140" s="14"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19">
       <c r="A141" s="10">
         <v>45873</v>
       </c>
@@ -25689,7 +25731,7 @@
       </c>
       <c r="S141" s="14"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19">
       <c r="A142" s="10">
         <v>45880</v>
       </c>
@@ -25746,7 +25788,7 @@
       </c>
       <c r="S142" s="14"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19">
       <c r="A143" s="10">
         <v>45887</v>
       </c>
@@ -25803,7 +25845,7 @@
       </c>
       <c r="S143" s="14"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19">
       <c r="A144" s="10">
         <v>45894</v>
       </c>
@@ -25860,7 +25902,7 @@
       </c>
       <c r="S144" s="14"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19">
       <c r="A145" s="10">
         <v>45901</v>
       </c>
@@ -25917,7 +25959,7 @@
       </c>
       <c r="S145" s="14"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19">
       <c r="A146" s="10">
         <v>45908</v>
       </c>
@@ -25974,7 +26016,7 @@
       </c>
       <c r="S146" s="14"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19">
       <c r="A147" s="10">
         <v>45915</v>
       </c>
@@ -26031,7 +26073,7 @@
       </c>
       <c r="S147" s="14"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19">
       <c r="A148" s="10">
         <v>45922</v>
       </c>
@@ -26088,7 +26130,7 @@
       </c>
       <c r="S148" s="14"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19">
       <c r="A149" s="10">
         <v>45929</v>
       </c>
@@ -26145,7 +26187,7 @@
       </c>
       <c r="S149" s="14"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19">
       <c r="A150" s="10">
         <v>45950</v>
       </c>
@@ -26202,7 +26244,7 @@
       </c>
       <c r="S150" s="14"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19">
       <c r="A151" s="10">
         <v>45957</v>
       </c>
@@ -26259,7 +26301,7 @@
       </c>
       <c r="S151" s="14"/>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19">
       <c r="A152" s="10">
         <v>45964</v>
       </c>
@@ -26316,7 +26358,7 @@
       </c>
       <c r="S152" s="14"/>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19">
       <c r="A153" s="10">
         <v>45971</v>
       </c>
@@ -26373,7 +26415,7 @@
       </c>
       <c r="S153" s="14"/>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19">
       <c r="A154" s="10">
         <v>45978</v>
       </c>
@@ -26430,7 +26472,7 @@
       </c>
       <c r="S154" s="14"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19">
       <c r="A155" s="10">
         <v>45985</v>
       </c>
@@ -26487,7 +26529,7 @@
       </c>
       <c r="S155" s="14"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19">
       <c r="A156" s="10">
         <v>45992</v>
       </c>
@@ -26544,7 +26586,7 @@
       </c>
       <c r="S156" s="14"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19">
       <c r="A157" s="10">
         <v>45999</v>
       </c>
@@ -26601,7 +26643,7 @@
       </c>
       <c r="S157" s="14"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19">
       <c r="A158" s="10">
         <v>46006</v>
       </c>
@@ -26658,7 +26700,7 @@
       </c>
       <c r="S158" s="14"/>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19">
       <c r="A159" s="10">
         <v>46013</v>
       </c>
@@ -26715,7 +26757,7 @@
       </c>
       <c r="S159" s="14"/>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19">
       <c r="A160" s="10">
         <v>46020</v>
       </c>
@@ -26772,7 +26814,7 @@
       </c>
       <c r="S160" s="14"/>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:19">
       <c r="A161" s="10">
         <v>46034</v>
       </c>
@@ -26829,7 +26871,7 @@
       </c>
       <c r="S161" s="14"/>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:19">
       <c r="A162" s="10">
         <v>46041</v>
       </c>
@@ -26886,7 +26928,7 @@
       </c>
       <c r="S162" s="14"/>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:19">
       <c r="A163" s="10">
         <v>46048</v>
       </c>
@@ -26943,7 +26985,7 @@
       </c>
       <c r="S163" s="14"/>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:19">
       <c r="A164" s="10">
         <v>46055</v>
       </c>
@@ -27000,7 +27042,7 @@
       </c>
       <c r="S164" s="14"/>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:19">
       <c r="A165" s="10">
         <v>46062</v>
       </c>
@@ -27057,7 +27099,7 @@
       </c>
       <c r="S165" s="14"/>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:19">
       <c r="A166" s="10">
         <v>46076</v>
       </c>
@@ -27113,7 +27155,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:19">
       <c r="A167" s="10">
         <v>46084</v>
       </c>
@@ -27169,7 +27211,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:19">
       <c r="A168" s="10">
         <v>46090</v>
       </c>
@@ -27225,7 +27267,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:19">
       <c r="A169" s="10">
         <v>46097</v>
       </c>
@@ -27281,7 +27323,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:19">
       <c r="A170" s="10">
         <v>46104</v>
       </c>
@@ -27337,7 +27379,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:19">
       <c r="A171" s="10">
         <v>46111</v>
       </c>
@@ -27393,7 +27435,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:19">
       <c r="A172" s="10">
         <v>46118</v>
       </c>
@@ -27449,7 +27491,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:19">
       <c r="A173" s="10">
         <v>46125</v>
       </c>
@@ -27505,7 +27547,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:19">
       <c r="A174" s="10">
         <v>46132</v>
       </c>
@@ -27561,7 +27603,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:19">
       <c r="A175" s="10">
         <v>46139</v>
       </c>
@@ -27617,7 +27659,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:19">
       <c r="A176" s="10">
         <v>46153</v>
       </c>
@@ -27673,7 +27715,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18">
       <c r="A177" s="10">
         <v>46160</v>
       </c>
@@ -27729,7 +27771,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18">
       <c r="A178" s="10">
         <v>46168</v>
       </c>
@@ -27785,7 +27827,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18">
       <c r="A179" s="10">
         <v>46174</v>
       </c>
@@ -27841,7 +27883,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18">
       <c r="A180" s="10">
         <v>46181</v>
       </c>
@@ -27897,7 +27939,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18">
       <c r="A181" s="10">
         <v>46188</v>
       </c>
@@ -27953,7 +27995,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18">
       <c r="A182" s="10">
         <v>46195</v>
       </c>
@@ -28009,7 +28051,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18">
       <c r="A183" s="10">
         <v>46202</v>
       </c>
@@ -28065,7 +28107,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18">
       <c r="A184" s="10">
         <v>46209</v>
       </c>
@@ -28121,7 +28163,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18">
       <c r="A185" s="10">
         <v>46216</v>
       </c>
@@ -28133,6 +28175,48 @@
       </c>
       <c r="D185" s="12" t="s">
         <v>22</v>
+      </c>
+      <c r="E185" s="13">
+        <v>4318</v>
+      </c>
+      <c r="F185" s="13">
+        <v>6734</v>
+      </c>
+      <c r="G185" s="13">
+        <v>8523</v>
+      </c>
+      <c r="H185" s="13">
+        <v>5426</v>
+      </c>
+      <c r="I185" s="13">
+        <v>6569</v>
+      </c>
+      <c r="J185" s="13">
+        <v>7266</v>
+      </c>
+      <c r="K185" s="13">
+        <v>3857</v>
+      </c>
+      <c r="L185" s="13">
+        <v>7554</v>
+      </c>
+      <c r="M185" s="13">
+        <v>5565</v>
+      </c>
+      <c r="N185" s="13">
+        <v>3636</v>
+      </c>
+      <c r="O185" s="13">
+        <v>5399</v>
+      </c>
+      <c r="P185" s="13">
+        <v>57</v>
+      </c>
+      <c r="Q185" s="13">
+        <v>239</v>
+      </c>
+      <c r="R185" s="13">
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
@@ -28148,14 +28232,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="2"/>
-    <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="9.08984375" style="2"/>
+    <col min="2" max="2" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
@@ -28163,7 +28247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -28184,9 +28268,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data_lake/freight/KOBC Container Composite Index.xlsx
+++ b/data_lake/freight/KOBC Container Composite Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5EC175-9CF7-4181-8488-3002799A56CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBBD7D0-04F4-489B-AEDE-749C32EF9022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -123,11 +123,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -172,14 +172,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -187,7 +187,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -220,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -243,31 +243,31 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -275,9 +275,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -295,7 +295,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -896,6 +896,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -903,7 +906,7 @@
             <c:numRef>
               <c:f>KCCI!$E$2:$E$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
@@ -1456,6 +1459,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>4318</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4204</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2051,6 +2057,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2058,7 +2067,7 @@
             <c:numRef>
               <c:f>KCCI!$F$2:$F$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
@@ -2611,6 +2620,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>6734</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3206,6 +3218,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3213,7 +3228,7 @@
             <c:numRef>
               <c:f>KCCI!$G$2:$G$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
@@ -3766,6 +3781,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>8523</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>8694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4361,6 +4379,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4368,7 +4389,7 @@
             <c:numRef>
               <c:f>KCCI!$H$2:$H$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
@@ -4921,6 +4942,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>5426</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5516,6 +5540,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5523,7 +5550,7 @@
             <c:numRef>
               <c:f>KCCI!$I$2:$I$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
@@ -6076,6 +6103,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>6569</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6671,6 +6701,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6678,7 +6711,7 @@
             <c:numRef>
               <c:f>KCCI!$J$2:$J$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
@@ -7231,6 +7264,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>7266</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>7269</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7828,6 +7864,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7835,7 +7874,7 @@
             <c:numRef>
               <c:f>KCCI!$K$2:$K$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
@@ -8388,6 +8427,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>3857</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8985,6 +9027,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8992,7 +9037,7 @@
             <c:numRef>
               <c:f>KCCI!$L$2:$L$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
@@ -9545,6 +9590,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>7554</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10142,6 +10190,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10149,7 +10200,7 @@
             <c:numRef>
               <c:f>KCCI!$M$2:$M$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
@@ -10702,6 +10753,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>5565</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11299,6 +11353,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11306,7 +11363,7 @@
             <c:numRef>
               <c:f>KCCI!$N$2:$N$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
@@ -11859,6 +11916,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>3636</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12456,6 +12516,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12463,7 +12526,7 @@
             <c:numRef>
               <c:f>KCCI!$O$2:$O$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
@@ -13016,6 +13079,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>5399</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13629,6 +13695,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13636,7 +13705,7 @@
             <c:numRef>
               <c:f>KCCI!$P$2:$P$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
@@ -14188,6 +14257,9 @@
                   <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="183">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="184">
                   <c:v>57</c:v>
                 </c:pt>
               </c:numCache>
@@ -14787,6 +14859,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14794,7 +14869,7 @@
             <c:numRef>
               <c:f>KCCI!$Q$2:$Q$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
@@ -15346,6 +15421,9 @@
                   <c:v>239</c:v>
                 </c:pt>
                 <c:pt idx="183">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="184">
                   <c:v>239</c:v>
                 </c:pt>
               </c:numCache>
@@ -15945,6 +16023,9 @@
                 <c:pt idx="183">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15952,7 +16033,7 @@
             <c:numRef>
               <c:f>KCCI!$R$2:$R$11164</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
@@ -16505,6 +16586,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>1137</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16604,7 +16688,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -16646,7 +16730,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -17379,9 +17463,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -17419,7 +17503,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -17525,7 +17609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -17667,7 +17751,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -17675,27 +17759,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S185"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <dimension ref="A1:S186"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.08984375" style="9"/>
+    <col min="1" max="1" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -17751,7 +17835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>44872</v>
       </c>
@@ -17808,7 +17892,7 @@
       </c>
       <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>44879</v>
       </c>
@@ -17865,7 +17949,7 @@
       </c>
       <c r="S3" s="14"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>44886</v>
       </c>
@@ -17922,7 +18006,7 @@
       </c>
       <c r="S4" s="14"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>44893</v>
       </c>
@@ -17979,7 +18063,7 @@
       </c>
       <c r="S5" s="14"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>44900</v>
       </c>
@@ -18036,7 +18120,7 @@
       </c>
       <c r="S6" s="14"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>44907</v>
       </c>
@@ -18093,7 +18177,7 @@
       </c>
       <c r="S7" s="14"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>44914</v>
       </c>
@@ -18150,7 +18234,7 @@
       </c>
       <c r="S8" s="14"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>44921</v>
       </c>
@@ -18207,7 +18291,7 @@
       </c>
       <c r="S9" s="14"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>44928</v>
       </c>
@@ -18264,7 +18348,7 @@
       </c>
       <c r="S10" s="14"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>44935</v>
       </c>
@@ -18321,7 +18405,7 @@
       </c>
       <c r="S11" s="14"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>44942</v>
       </c>
@@ -18378,7 +18462,7 @@
       </c>
       <c r="S12" s="14"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>44951</v>
       </c>
@@ -18435,7 +18519,7 @@
       </c>
       <c r="S13" s="14"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>44956</v>
       </c>
@@ -18492,7 +18576,7 @@
       </c>
       <c r="S14" s="14"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>44963</v>
       </c>
@@ -18549,7 +18633,7 @@
       </c>
       <c r="S15" s="14"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>44970</v>
       </c>
@@ -18606,7 +18690,7 @@
       </c>
       <c r="S16" s="14"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>44977</v>
       </c>
@@ -18663,7 +18747,7 @@
       </c>
       <c r="S17" s="14"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>44984</v>
       </c>
@@ -18720,7 +18804,7 @@
       </c>
       <c r="S18" s="14"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>44991</v>
       </c>
@@ -18777,7 +18861,7 @@
       </c>
       <c r="S19" s="14"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>44998</v>
       </c>
@@ -18834,7 +18918,7 @@
       </c>
       <c r="S20" s="14"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>45005</v>
       </c>
@@ -18891,7 +18975,7 @@
       </c>
       <c r="S21" s="14"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>45012</v>
       </c>
@@ -18948,7 +19032,7 @@
       </c>
       <c r="S22" s="14"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>45019</v>
       </c>
@@ -19005,7 +19089,7 @@
       </c>
       <c r="S23" s="14"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>45026</v>
       </c>
@@ -19062,7 +19146,7 @@
       </c>
       <c r="S24" s="14"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>45033</v>
       </c>
@@ -19119,7 +19203,7 @@
       </c>
       <c r="S25" s="14"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>45040</v>
       </c>
@@ -19176,7 +19260,7 @@
       </c>
       <c r="S26" s="14"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>45048</v>
       </c>
@@ -19233,7 +19317,7 @@
       </c>
       <c r="S27" s="14"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>45054</v>
       </c>
@@ -19290,7 +19374,7 @@
       </c>
       <c r="S28" s="14"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>45061</v>
       </c>
@@ -19347,7 +19431,7 @@
       </c>
       <c r="S29" s="14"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>45068</v>
       </c>
@@ -19404,7 +19488,7 @@
       </c>
       <c r="S30" s="14"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>45076</v>
       </c>
@@ -19461,7 +19545,7 @@
       </c>
       <c r="S31" s="14"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>45082</v>
       </c>
@@ -19518,7 +19602,7 @@
       </c>
       <c r="S32" s="14"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>45089</v>
       </c>
@@ -19575,7 +19659,7 @@
       </c>
       <c r="S33" s="14"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>45096</v>
       </c>
@@ -19632,7 +19716,7 @@
       </c>
       <c r="S34" s="14"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>45103</v>
       </c>
@@ -19689,7 +19773,7 @@
       </c>
       <c r="S35" s="14"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>45110</v>
       </c>
@@ -19746,7 +19830,7 @@
       </c>
       <c r="S36" s="14"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>45117</v>
       </c>
@@ -19803,7 +19887,7 @@
       </c>
       <c r="S37" s="14"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>45124</v>
       </c>
@@ -19860,7 +19944,7 @@
       </c>
       <c r="S38" s="14"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>45131</v>
       </c>
@@ -19917,7 +20001,7 @@
       </c>
       <c r="S39" s="14"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>45138</v>
       </c>
@@ -19974,7 +20058,7 @@
       </c>
       <c r="S40" s="14"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>45145</v>
       </c>
@@ -20031,7 +20115,7 @@
       </c>
       <c r="S41" s="14"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>45152</v>
       </c>
@@ -20088,7 +20172,7 @@
       </c>
       <c r="S42" s="14"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>45159</v>
       </c>
@@ -20145,7 +20229,7 @@
       </c>
       <c r="S43" s="14"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>45166</v>
       </c>
@@ -20202,7 +20286,7 @@
       </c>
       <c r="S44" s="14"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>45173</v>
       </c>
@@ -20259,7 +20343,7 @@
       </c>
       <c r="S45" s="14"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>45180</v>
       </c>
@@ -20316,7 +20400,7 @@
       </c>
       <c r="S46" s="14"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>45187</v>
       </c>
@@ -20373,7 +20457,7 @@
       </c>
       <c r="S47" s="14"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>45194</v>
       </c>
@@ -20430,7 +20514,7 @@
       </c>
       <c r="S48" s="14"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>45209</v>
       </c>
@@ -20487,7 +20571,7 @@
       </c>
       <c r="S49" s="14"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>45215</v>
       </c>
@@ -20544,7 +20628,7 @@
       </c>
       <c r="S50" s="14"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>45222</v>
       </c>
@@ -20601,7 +20685,7 @@
       </c>
       <c r="S51" s="14"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>45229</v>
       </c>
@@ -20658,7 +20742,7 @@
       </c>
       <c r="S52" s="14"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>45236</v>
       </c>
@@ -20715,7 +20799,7 @@
       </c>
       <c r="S53" s="14"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>45243</v>
       </c>
@@ -20772,7 +20856,7 @@
       </c>
       <c r="S54" s="14"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>45250</v>
       </c>
@@ -20829,7 +20913,7 @@
       </c>
       <c r="S55" s="14"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>45257</v>
       </c>
@@ -20886,7 +20970,7 @@
       </c>
       <c r="S56" s="14"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>45264</v>
       </c>
@@ -20943,7 +21027,7 @@
       </c>
       <c r="S57" s="14"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="10">
         <v>45271</v>
       </c>
@@ -21000,7 +21084,7 @@
       </c>
       <c r="S58" s="14"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>45278</v>
       </c>
@@ -21057,7 +21141,7 @@
       </c>
       <c r="S59" s="14"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>45286</v>
       </c>
@@ -21114,7 +21198,7 @@
       </c>
       <c r="S60" s="14"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>45293</v>
       </c>
@@ -21171,7 +21255,7 @@
       </c>
       <c r="S61" s="14"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
         <v>45299</v>
       </c>
@@ -21228,7 +21312,7 @@
       </c>
       <c r="S62" s="14"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>45306</v>
       </c>
@@ -21285,7 +21369,7 @@
       </c>
       <c r="S63" s="14"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="10">
         <v>45313</v>
       </c>
@@ -21342,7 +21426,7 @@
       </c>
       <c r="S64" s="14"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>45320</v>
       </c>
@@ -21399,7 +21483,7 @@
       </c>
       <c r="S65" s="14"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="10">
         <v>45327</v>
       </c>
@@ -21456,7 +21540,7 @@
       </c>
       <c r="S66" s="14"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="10">
         <v>45335</v>
       </c>
@@ -21513,7 +21597,7 @@
       </c>
       <c r="S67" s="14"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="10">
         <v>45341</v>
       </c>
@@ -21570,7 +21654,7 @@
       </c>
       <c r="S68" s="14"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="10">
         <v>45348</v>
       </c>
@@ -21627,7 +21711,7 @@
       </c>
       <c r="S69" s="14"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="10">
         <v>45355</v>
       </c>
@@ -21684,7 +21768,7 @@
       </c>
       <c r="S70" s="14"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="10">
         <v>45362</v>
       </c>
@@ -21741,7 +21825,7 @@
       </c>
       <c r="S71" s="14"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="10">
         <v>45369</v>
       </c>
@@ -21798,7 +21882,7 @@
       </c>
       <c r="S72" s="14"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="10">
         <v>45376</v>
       </c>
@@ -21855,7 +21939,7 @@
       </c>
       <c r="S73" s="14"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="10">
         <v>45383</v>
       </c>
@@ -21912,7 +21996,7 @@
       </c>
       <c r="S74" s="14"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="10">
         <v>45390</v>
       </c>
@@ -21969,7 +22053,7 @@
       </c>
       <c r="S75" s="14"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="10">
         <v>45397</v>
       </c>
@@ -22026,7 +22110,7 @@
       </c>
       <c r="S76" s="14"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="10">
         <v>45404</v>
       </c>
@@ -22083,7 +22167,7 @@
       </c>
       <c r="S77" s="14"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="10">
         <v>45411</v>
       </c>
@@ -22140,7 +22224,7 @@
       </c>
       <c r="S78" s="14"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="10">
         <v>45419</v>
       </c>
@@ -22197,7 +22281,7 @@
       </c>
       <c r="S79" s="14"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="10">
         <v>45425</v>
       </c>
@@ -22254,7 +22338,7 @@
       </c>
       <c r="S80" s="14"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="10">
         <v>45432</v>
       </c>
@@ -22311,7 +22395,7 @@
       </c>
       <c r="S81" s="14"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="10">
         <v>45439</v>
       </c>
@@ -22368,7 +22452,7 @@
       </c>
       <c r="S82" s="14"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="10">
         <v>45446</v>
       </c>
@@ -22425,7 +22509,7 @@
       </c>
       <c r="S83" s="14"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="10">
         <v>45453</v>
       </c>
@@ -22482,7 +22566,7 @@
       </c>
       <c r="S84" s="14"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="10">
         <v>45460</v>
       </c>
@@ -22539,7 +22623,7 @@
       </c>
       <c r="S85" s="14"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="10">
         <v>45467</v>
       </c>
@@ -22596,7 +22680,7 @@
       </c>
       <c r="S86" s="14"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" s="10">
         <v>45474</v>
       </c>
@@ -22653,7 +22737,7 @@
       </c>
       <c r="S87" s="14"/>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" s="10">
         <v>45481</v>
       </c>
@@ -22710,7 +22794,7 @@
       </c>
       <c r="S88" s="14"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" s="10">
         <v>45488</v>
       </c>
@@ -22767,7 +22851,7 @@
       </c>
       <c r="S89" s="14"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="10">
         <v>45495</v>
       </c>
@@ -22824,7 +22908,7 @@
       </c>
       <c r="S90" s="14"/>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" s="10">
         <v>45502</v>
       </c>
@@ -22881,7 +22965,7 @@
       </c>
       <c r="S91" s="14"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="10">
         <v>45509</v>
       </c>
@@ -22938,7 +23022,7 @@
       </c>
       <c r="S92" s="14"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="10">
         <v>45516</v>
       </c>
@@ -22995,7 +23079,7 @@
       </c>
       <c r="S93" s="14"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" s="10">
         <v>45523</v>
       </c>
@@ -23052,7 +23136,7 @@
       </c>
       <c r="S94" s="14"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="10">
         <v>45530</v>
       </c>
@@ -23109,7 +23193,7 @@
       </c>
       <c r="S95" s="14"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" s="10">
         <v>45537</v>
       </c>
@@ -23166,7 +23250,7 @@
       </c>
       <c r="S96" s="14"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" s="10">
         <v>45544</v>
       </c>
@@ -23223,7 +23307,7 @@
       </c>
       <c r="S97" s="14"/>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" s="10">
         <v>45558</v>
       </c>
@@ -23280,7 +23364,7 @@
       </c>
       <c r="S98" s="14"/>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" s="10">
         <v>45565</v>
       </c>
@@ -23337,7 +23421,7 @@
       </c>
       <c r="S99" s="14"/>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" s="10">
         <v>45572</v>
       </c>
@@ -23394,7 +23478,7 @@
       </c>
       <c r="S100" s="14"/>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" s="10">
         <v>45579</v>
       </c>
@@ -23451,7 +23535,7 @@
       </c>
       <c r="S101" s="14"/>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" s="10">
         <v>45586</v>
       </c>
@@ -23508,7 +23592,7 @@
       </c>
       <c r="S102" s="14"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" s="10">
         <v>45593</v>
       </c>
@@ -23565,7 +23649,7 @@
       </c>
       <c r="S103" s="14"/>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" s="10">
         <v>45600</v>
       </c>
@@ -23622,7 +23706,7 @@
       </c>
       <c r="S104" s="14"/>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" s="10">
         <v>45607</v>
       </c>
@@ -23679,7 +23763,7 @@
       </c>
       <c r="S105" s="14"/>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" s="10">
         <v>45614</v>
       </c>
@@ -23736,7 +23820,7 @@
       </c>
       <c r="S106" s="14"/>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" s="10">
         <v>45621</v>
       </c>
@@ -23793,7 +23877,7 @@
       </c>
       <c r="S107" s="14"/>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" s="10">
         <v>45628</v>
       </c>
@@ -23850,7 +23934,7 @@
       </c>
       <c r="S108" s="14"/>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" s="10">
         <v>45635</v>
       </c>
@@ -23907,7 +23991,7 @@
       </c>
       <c r="S109" s="14"/>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" s="10">
         <v>45642</v>
       </c>
@@ -23964,7 +24048,7 @@
       </c>
       <c r="S110" s="14"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" s="10">
         <v>45649</v>
       </c>
@@ -24021,7 +24105,7 @@
       </c>
       <c r="S111" s="14"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" s="10">
         <v>45656</v>
       </c>
@@ -24078,7 +24162,7 @@
       </c>
       <c r="S112" s="14"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" s="10">
         <v>45663</v>
       </c>
@@ -24135,7 +24219,7 @@
       </c>
       <c r="S113" s="14"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" s="10">
         <v>45670</v>
       </c>
@@ -24192,7 +24276,7 @@
       </c>
       <c r="S114" s="14"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" s="10">
         <v>45677</v>
       </c>
@@ -24249,7 +24333,7 @@
       </c>
       <c r="S115" s="14"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" s="10">
         <v>45691</v>
       </c>
@@ -24306,7 +24390,7 @@
       </c>
       <c r="S116" s="14"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" s="10">
         <v>45698</v>
       </c>
@@ -24363,7 +24447,7 @@
       </c>
       <c r="S117" s="14"/>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" s="10">
         <v>45705</v>
       </c>
@@ -24420,7 +24504,7 @@
       </c>
       <c r="S118" s="14"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" s="10">
         <v>45712</v>
       </c>
@@ -24477,7 +24561,7 @@
       </c>
       <c r="S119" s="14"/>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" s="10">
         <v>45720</v>
       </c>
@@ -24534,7 +24618,7 @@
       </c>
       <c r="S120" s="14"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" s="10">
         <v>45726</v>
       </c>
@@ -24591,7 +24675,7 @@
       </c>
       <c r="S121" s="14"/>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" s="10">
         <v>45733</v>
       </c>
@@ -24648,7 +24732,7 @@
       </c>
       <c r="S122" s="14"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" s="10">
         <v>45740</v>
       </c>
@@ -24705,7 +24789,7 @@
       </c>
       <c r="S123" s="14"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" s="10">
         <v>45747</v>
       </c>
@@ -24762,7 +24846,7 @@
       </c>
       <c r="S124" s="14"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" s="10">
         <v>45754</v>
       </c>
@@ -24819,7 +24903,7 @@
       </c>
       <c r="S125" s="14"/>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" s="10">
         <v>45761</v>
       </c>
@@ -24876,7 +24960,7 @@
       </c>
       <c r="S126" s="14"/>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" s="10">
         <v>45768</v>
       </c>
@@ -24933,7 +25017,7 @@
       </c>
       <c r="S127" s="14"/>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" s="10">
         <v>45775</v>
       </c>
@@ -24990,7 +25074,7 @@
       </c>
       <c r="S128" s="14"/>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" s="10">
         <v>45789</v>
       </c>
@@ -25047,7 +25131,7 @@
       </c>
       <c r="S129" s="14"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" s="10">
         <v>45796</v>
       </c>
@@ -25104,7 +25188,7 @@
       </c>
       <c r="S130" s="14"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" s="10">
         <v>45803</v>
       </c>
@@ -25161,7 +25245,7 @@
       </c>
       <c r="S131" s="14"/>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" s="10">
         <v>45810</v>
       </c>
@@ -25218,7 +25302,7 @@
       </c>
       <c r="S132" s="14"/>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" s="10">
         <v>45817</v>
       </c>
@@ -25275,7 +25359,7 @@
       </c>
       <c r="S133" s="14"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" s="10">
         <v>45824</v>
       </c>
@@ -25332,7 +25416,7 @@
       </c>
       <c r="S134" s="14"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" s="10">
         <v>45831</v>
       </c>
@@ -25389,7 +25473,7 @@
       </c>
       <c r="S135" s="14"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" s="10">
         <v>45838</v>
       </c>
@@ -25446,7 +25530,7 @@
       </c>
       <c r="S136" s="14"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" s="10">
         <v>45845</v>
       </c>
@@ -25503,7 +25587,7 @@
       </c>
       <c r="S137" s="14"/>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" s="10">
         <v>45852</v>
       </c>
@@ -25560,7 +25644,7 @@
       </c>
       <c r="S138" s="14"/>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" s="10">
         <v>45859</v>
       </c>
@@ -25617,7 +25701,7 @@
       </c>
       <c r="S139" s="14"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" s="10">
         <v>45866</v>
       </c>
@@ -25674,7 +25758,7 @@
       </c>
       <c r="S140" s="14"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" s="10">
         <v>45873</v>
       </c>
@@ -25731,7 +25815,7 @@
       </c>
       <c r="S141" s="14"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" s="10">
         <v>45880</v>
       </c>
@@ -25788,7 +25872,7 @@
       </c>
       <c r="S142" s="14"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" s="10">
         <v>45887</v>
       </c>
@@ -25845,7 +25929,7 @@
       </c>
       <c r="S143" s="14"/>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" s="10">
         <v>45894</v>
       </c>
@@ -25902,7 +25986,7 @@
       </c>
       <c r="S144" s="14"/>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" s="10">
         <v>45901</v>
       </c>
@@ -25959,7 +26043,7 @@
       </c>
       <c r="S145" s="14"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" s="10">
         <v>45908</v>
       </c>
@@ -26016,7 +26100,7 @@
       </c>
       <c r="S146" s="14"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" s="10">
         <v>45915</v>
       </c>
@@ -26073,7 +26157,7 @@
       </c>
       <c r="S147" s="14"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" s="10">
         <v>45922</v>
       </c>
@@ -26130,7 +26214,7 @@
       </c>
       <c r="S148" s="14"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" s="10">
         <v>45929</v>
       </c>
@@ -26187,7 +26271,7 @@
       </c>
       <c r="S149" s="14"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" s="10">
         <v>45950</v>
       </c>
@@ -26244,7 +26328,7 @@
       </c>
       <c r="S150" s="14"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" s="10">
         <v>45957</v>
       </c>
@@ -26301,7 +26385,7 @@
       </c>
       <c r="S151" s="14"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" s="10">
         <v>45964</v>
       </c>
@@ -26358,7 +26442,7 @@
       </c>
       <c r="S152" s="14"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" s="10">
         <v>45971</v>
       </c>
@@ -26415,7 +26499,7 @@
       </c>
       <c r="S153" s="14"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" s="10">
         <v>45978</v>
       </c>
@@ -26472,7 +26556,7 @@
       </c>
       <c r="S154" s="14"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" s="10">
         <v>45985</v>
       </c>
@@ -26529,7 +26613,7 @@
       </c>
       <c r="S155" s="14"/>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" s="10">
         <v>45992</v>
       </c>
@@ -26586,7 +26670,7 @@
       </c>
       <c r="S156" s="14"/>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" s="10">
         <v>45999</v>
       </c>
@@ -26643,7 +26727,7 @@
       </c>
       <c r="S157" s="14"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" s="10">
         <v>46006</v>
       </c>
@@ -26700,7 +26784,7 @@
       </c>
       <c r="S158" s="14"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159" s="10">
         <v>46013</v>
       </c>
@@ -26757,7 +26841,7 @@
       </c>
       <c r="S159" s="14"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160" s="10">
         <v>46020</v>
       </c>
@@ -26814,7 +26898,7 @@
       </c>
       <c r="S160" s="14"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161" s="10">
         <v>46034</v>
       </c>
@@ -26871,7 +26955,7 @@
       </c>
       <c r="S161" s="14"/>
     </row>
-    <row r="162" spans="1:19">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A162" s="10">
         <v>46041</v>
       </c>
@@ -26928,7 +27012,7 @@
       </c>
       <c r="S162" s="14"/>
     </row>
-    <row r="163" spans="1:19">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A163" s="10">
         <v>46048</v>
       </c>
@@ -26985,7 +27069,7 @@
       </c>
       <c r="S163" s="14"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A164" s="10">
         <v>46055</v>
       </c>
@@ -27042,7 +27126,7 @@
       </c>
       <c r="S164" s="14"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A165" s="10">
         <v>46062</v>
       </c>
@@ -27099,7 +27183,7 @@
       </c>
       <c r="S165" s="14"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A166" s="10">
         <v>46076</v>
       </c>
@@ -27155,7 +27239,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A167" s="10">
         <v>46084</v>
       </c>
@@ -27211,7 +27295,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="168" spans="1:19">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A168" s="10">
         <v>46090</v>
       </c>
@@ -27267,7 +27351,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="169" spans="1:19">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A169" s="10">
         <v>46097</v>
       </c>
@@ -27323,7 +27407,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A170" s="10">
         <v>46104</v>
       </c>
@@ -27379,7 +27463,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A171" s="10">
         <v>46111</v>
       </c>
@@ -27435,7 +27519,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A172" s="10">
         <v>46118</v>
       </c>
@@ -27491,7 +27575,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A173" s="10">
         <v>46125</v>
       </c>
@@ -27547,7 +27631,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="174" spans="1:19">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A174" s="10">
         <v>46132</v>
       </c>
@@ -27603,7 +27687,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="175" spans="1:19">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A175" s="10">
         <v>46139</v>
       </c>
@@ -27659,7 +27743,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="176" spans="1:19">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A176" s="10">
         <v>46153</v>
       </c>
@@ -27715,7 +27799,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A177" s="10">
         <v>46160</v>
       </c>
@@ -27771,7 +27855,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A178" s="10">
         <v>46168</v>
       </c>
@@ -27827,7 +27911,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A179" s="10">
         <v>46174</v>
       </c>
@@ -27883,7 +27967,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A180" s="10">
         <v>46181</v>
       </c>
@@ -27939,7 +28023,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A181" s="10">
         <v>46188</v>
       </c>
@@ -27995,7 +28079,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A182" s="10">
         <v>46195</v>
       </c>
@@ -28051,7 +28135,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="183" spans="1:18">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A183" s="10">
         <v>46202</v>
       </c>
@@ -28107,7 +28191,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A184" s="10">
         <v>46209</v>
       </c>
@@ -28163,7 +28247,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A185" s="10">
         <v>46216</v>
       </c>
@@ -28217,6 +28301,62 @@
       </c>
       <c r="R185" s="13">
         <v>1137</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A186" s="10">
+        <v>46223</v>
+      </c>
+      <c r="B186" s="10">
+        <v>46223</v>
+      </c>
+      <c r="C186" s="11">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E186" s="13">
+        <v>4204</v>
+      </c>
+      <c r="F186" s="13">
+        <v>6385</v>
+      </c>
+      <c r="G186" s="13">
+        <v>8694</v>
+      </c>
+      <c r="H186" s="13">
+        <v>5184</v>
+      </c>
+      <c r="I186" s="13">
+        <v>6313</v>
+      </c>
+      <c r="J186" s="13">
+        <v>7269</v>
+      </c>
+      <c r="K186" s="13">
+        <v>4086</v>
+      </c>
+      <c r="L186" s="13">
+        <v>6881</v>
+      </c>
+      <c r="M186" s="13">
+        <v>5231</v>
+      </c>
+      <c r="N186" s="13">
+        <v>3644</v>
+      </c>
+      <c r="O186" s="13">
+        <v>5298</v>
+      </c>
+      <c r="P186" s="13">
+        <v>57</v>
+      </c>
+      <c r="Q186" s="13">
+        <v>239</v>
+      </c>
+      <c r="R186" s="13">
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -28232,14 +28372,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="2"/>
-    <col min="2" max="2" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.08984375" style="2"/>
+    <col min="1" max="1" width="9.109375" style="2"/>
+    <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
@@ -28247,7 +28387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -28268,9 +28408,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.08984375" style="1"/>
+    <col min="1" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data_lake/freight/KOBC Container Composite Index.xlsx
+++ b/data_lake/freight/KOBC Container Composite Index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBBD7D0-04F4-489B-AEDE-749C32EF9022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86404CE-67C1-4DDB-B34E-301E78C0BCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -899,6 +899,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1462,6 +1465,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>4204</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2060,6 +2066,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2623,6 +2632,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>6385</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3221,6 +3233,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3784,6 +3799,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>8694</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>8758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4382,6 +4400,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4945,6 +4966,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>5184</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5543,6 +5567,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6106,6 +6133,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>6313</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6704,6 +6734,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7267,6 +7300,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>7269</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>7455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7867,6 +7903,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8430,6 +8469,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>4086</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9030,6 +9072,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9593,6 +9638,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>6881</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6590</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10193,6 +10241,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10756,6 +10807,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>5231</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4925</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11356,6 +11410,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11919,6 +11976,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>3644</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3662</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12519,6 +12579,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13082,6 +13145,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>5298</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5290</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13698,6 +13764,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14261,6 +14330,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14862,6 +14934,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15424,6 +15499,9 @@
                   <c:v>239</c:v>
                 </c:pt>
                 <c:pt idx="184">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="185">
                   <c:v>239</c:v>
                 </c:pt>
               </c:numCache>
@@ -16026,6 +16104,9 @@
                 <c:pt idx="184">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="185">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16589,6 +16670,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>1136</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16617,7 +16701,7 @@
         <c:axId val="910378303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="46387"/>
+          <c:max val="47118"/>
           <c:min val="44927"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -16651,7 +16735,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
@@ -16711,7 +16795,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
@@ -16753,7 +16837,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
@@ -16812,7 +16896,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
@@ -16848,7 +16932,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1050">
-          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -17429,10 +17513,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17759,7 +17843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S186"/>
+  <dimension ref="A1:S187"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
@@ -28357,6 +28441,62 @@
       </c>
       <c r="R186" s="13">
         <v>1136</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A187" s="10">
+        <v>46230</v>
+      </c>
+      <c r="B187" s="10">
+        <v>46230</v>
+      </c>
+      <c r="C187" s="11">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E187" s="13">
+        <v>4123</v>
+      </c>
+      <c r="F187" s="13">
+        <v>6115</v>
+      </c>
+      <c r="G187" s="13">
+        <v>8758</v>
+      </c>
+      <c r="H187" s="13">
+        <v>4947</v>
+      </c>
+      <c r="I187" s="13">
+        <v>6107</v>
+      </c>
+      <c r="J187" s="13">
+        <v>7455</v>
+      </c>
+      <c r="K187" s="13">
+        <v>4206</v>
+      </c>
+      <c r="L187" s="13">
+        <v>6590</v>
+      </c>
+      <c r="M187" s="13">
+        <v>4925</v>
+      </c>
+      <c r="N187" s="13">
+        <v>3662</v>
+      </c>
+      <c r="O187" s="13">
+        <v>5290</v>
+      </c>
+      <c r="P187" s="13">
+        <v>55</v>
+      </c>
+      <c r="Q187" s="13">
+        <v>239</v>
+      </c>
+      <c r="R187" s="13">
+        <v>1149</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/KOBC Container Composite Index.xlsx
+++ b/data_lake/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86404CE-67C1-4DDB-B34E-301E78C0BCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462143B3-373B-4726-886B-3096C7FFB5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -902,6 +902,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1468,6 +1471,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>4123</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2069,6 +2075,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2635,6 +2644,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>6115</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3236,6 +3248,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3802,6 +3817,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>8758</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>8986</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4403,6 +4421,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4969,6 +4990,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>4947</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5570,6 +5594,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6136,6 +6163,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>6107</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5933</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6737,6 +6767,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7303,6 +7336,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>7455</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>7587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7906,6 +7942,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8472,6 +8511,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>4206</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9075,6 +9117,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9641,6 +9686,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>6590</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6406</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10244,6 +10292,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10810,6 +10861,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>4925</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11413,6 +11467,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11979,6 +12036,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>3662</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3760</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12582,6 +12642,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13148,6 +13211,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>5290</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13767,6 +13833,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14333,6 +14402,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14937,6 +15009,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15503,6 +15578,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16107,6 +16185,9 @@
                 <c:pt idx="185">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="186">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16673,6 +16754,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>1149</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17843,7 +17927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S187"/>
+  <dimension ref="A1:S188"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
@@ -28497,6 +28581,62 @@
       </c>
       <c r="R187" s="13">
         <v>1149</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A188" s="10">
+        <v>46237</v>
+      </c>
+      <c r="B188" s="10">
+        <v>46237</v>
+      </c>
+      <c r="C188" s="11">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E188" s="13">
+        <v>4138</v>
+      </c>
+      <c r="F188" s="13">
+        <v>6172</v>
+      </c>
+      <c r="G188" s="13">
+        <v>8986</v>
+      </c>
+      <c r="H188" s="13">
+        <v>4884</v>
+      </c>
+      <c r="I188" s="13">
+        <v>5933</v>
+      </c>
+      <c r="J188" s="13">
+        <v>7587</v>
+      </c>
+      <c r="K188" s="13">
+        <v>4309</v>
+      </c>
+      <c r="L188" s="13">
+        <v>6406</v>
+      </c>
+      <c r="M188" s="13">
+        <v>4819</v>
+      </c>
+      <c r="N188" s="13">
+        <v>3760</v>
+      </c>
+      <c r="O188" s="13">
+        <v>5244</v>
+      </c>
+      <c r="P188" s="13">
+        <v>56</v>
+      </c>
+      <c r="Q188" s="13">
+        <v>238</v>
+      </c>
+      <c r="R188" s="13">
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
